--- a/12. NCU_Validated_Women's Aliases_Master.xlsx
+++ b/12. NCU_Validated_Women's Aliases_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="46">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -151,6 +151,12 @@
   </si>
   <si>
     <t>Isabelle Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ellen Taylor Skilling </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ellen Skilling </t>
   </si>
 </sst>
 </file>
@@ -551,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35" style="7" customWidth="1"/>
@@ -840,6 +846,20 @@
         <v>5</v>
       </c>
     </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A3:D16">
     <sortCondition ref="A2"/>

--- a/12. NCU_Validated_Women's Aliases_Master.xlsx
+++ b/12. NCU_Validated_Women's Aliases_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD01D18F-01EA-428B-AB1E-376FFF934F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0768F458-79CC-47A7-8962-B328F29D5972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15645" yWindow="4545" windowWidth="20085" windowHeight="16335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="78">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -97,6 +97,36 @@
     <t>Anna Lunney</t>
   </si>
   <si>
+    <t>Elowyn Coyle</t>
+  </si>
+  <si>
+    <t>Anna Megarell</t>
+  </si>
+  <si>
+    <t>Ellie Skilling</t>
+  </si>
+  <si>
+    <t>E Stoddart</t>
+  </si>
+  <si>
+    <t>Taila Hurleu</t>
+  </si>
+  <si>
+    <t>Ruby Siken</t>
+  </si>
+  <si>
+    <t>René Margot Rankin</t>
+  </si>
+  <si>
+    <t>Daisy May Mullin</t>
+  </si>
+  <si>
+    <t>Emily Jean Stewart</t>
+  </si>
+  <si>
+    <t>Freya Beth Nelson</t>
+  </si>
+  <si>
     <t>Alexandra Atkinson</t>
   </si>
   <si>
@@ -160,32 +190,78 @@
     <t>Anna Lunny</t>
   </si>
   <si>
+    <t>Elowen Coyle</t>
+  </si>
+  <si>
+    <t>Anna Megarrell</t>
+  </si>
+  <si>
+    <t>Ellen Skilling</t>
+  </si>
+  <si>
+    <t>Ella Stoddart</t>
+  </si>
+  <si>
+    <t>Taila Hurley</t>
+  </si>
+  <si>
+    <t>Ruby Aiken</t>
+  </si>
+  <si>
+    <t>René Rankin</t>
+  </si>
+  <si>
+    <t>Daisy Mullin</t>
+  </si>
+  <si>
+    <t>Emily Stewart</t>
+  </si>
+  <si>
+    <t>Freya Nelson</t>
+  </si>
+  <si>
     <t>Verified in Database</t>
   </si>
   <si>
     <t>Validated</t>
   </si>
   <si>
+    <t>Verified</t>
+  </si>
+  <si>
     <t>Standard baseline mapping rule</t>
   </si>
   <si>
     <t>Added as per Wylie request</t>
+  </si>
+  <si>
+    <t>Added as per Wylie request (Spelling fix)</t>
+  </si>
+  <si>
+    <t>Added as per Wylie request (Nickname fix)</t>
+  </si>
+  <si>
+    <t>Added as per Wylie request (Scorecard initial fix)</t>
+  </si>
+  <si>
+    <t>Sport80 payment typo (u/y keyboard slip)</t>
+  </si>
+  <si>
+    <t>Sport80 payment typo (S/A keyboard slip)</t>
+  </si>
+  <si>
+    <t>Sport80 payment variation (middle name included)</t>
+  </si>
+  <si>
+    <t>Sport80 middle name mapping</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -213,9 +289,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,26 +595,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -548,13 +623,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -562,13 +637,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -576,13 +651,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -590,13 +665,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -604,13 +679,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -618,13 +693,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -632,13 +707,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -646,13 +721,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -660,13 +735,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -674,13 +749,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -688,13 +763,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -702,13 +777,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -716,13 +791,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -730,13 +805,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -744,13 +819,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -758,13 +833,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -772,13 +847,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -786,13 +861,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -800,13 +875,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -814,13 +889,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -828,13 +903,153 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/12. NCU_Validated_Women's Aliases_Master.xlsx
+++ b/12. NCU_Validated_Women's Aliases_Master.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +28,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -57,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -427,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -437,22 +443,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Input Name (Scorecard/Stats)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Official Registered Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Ledger Status Verification</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1137,6 +1143,28 @@
       <c r="D32" t="inlineStr">
         <is>
           <t>Sport80 middle name mapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sarah G</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sarah Gallagher</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Verified in Database</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Holywood 1881 scorer / player alias</t>
         </is>
       </c>
     </row>
